--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BOSCO MÉRIDA PATRIMONIO DE LA HUMANIDAD.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BOSCO MÉRIDA PATRIMONIO DE LA HUMANIDAD.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3709</v>
+        <v>0.4459</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4682</v>
+        <v>-0.1139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8391</v>
+        <v>0.5598</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.8299</v>
+        <v>-2.758</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.3844</v>
+        <v>-1.2257</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.4455</v>
+        <v>-1.5323</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.4851</v>
+        <v>-1.2739</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.6051</v>
+        <v>-1.3955</v>
       </c>
       <c r="L2" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3448</v>
+        <v>-1.4841</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2207</v>
+        <v>0.1698</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.5655</v>
+        <v>-1.6539</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4017</v>
+        <v>3.3197</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3587</v>
+        <v>2.3332</v>
       </c>
       <c r="U2" t="n">
-        <v>1.043</v>
+        <v>0.9865</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6593</v>
+        <v>2.7216</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1697</v>
+        <v>0.3273</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9211</v>
+        <v>1.4104</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7514</v>
+        <v>-1.0831</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.5164</v>
+        <v>-2.4683</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.6051</v>
+        <v>-2.5672</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0887</v>
+        <v>0.0989</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1213</v>
+        <v>0.1328</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.7687</v>
+        <v>-1.6265</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6474</v>
+        <v>1.7594</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3951</v>
+        <v>-2.6011</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8365</v>
+        <v>-0.9407</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5586</v>
+        <v>-1.6604</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2009</v>
+        <v>3.1158</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.0333</v>
+        <v>-1.9844</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.6759</v>
+        <v>-1.6077</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3574</v>
+        <v>-0.3767</v>
       </c>
       <c r="V3" t="n">
-        <v>3.519</v>
+        <v>3.6116</v>
       </c>
       <c r="W3" t="n">
-        <v>4.7188</v>
+        <v>4.8326</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="4">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1538</v>
+        <v>-0.1727</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0445</v>
+        <v>-0.0413</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1093</v>
+        <v>-0.1314</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3087</v>
+        <v>-0.3242</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1799</v>
+        <v>-0.1847</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3287</v>
+        <v>-0.3447</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0451</v>
+        <v>-0.0433</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0193</v>
+        <v>0.0186</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3329</v>
+        <v>-0.2823</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8772</v>
+        <v>-0.5144</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5443</v>
+        <v>0.2321</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7755</v>
+        <v>-0.7861</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1735</v>
+        <v>-1.1669</v>
       </c>
       <c r="I5" t="n">
-        <v>0.398</v>
+        <v>0.3808</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6909</v>
+        <v>1.8756</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0054</v>
+        <v>0.1002</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6855</v>
+        <v>1.7754</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4663</v>
+        <v>-2.6617</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1789</v>
+        <v>-1.2671</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2874</v>
+        <v>-1.3946</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2009</v>
+        <v>3.1158</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3168</v>
+        <v>-0.3152</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1265</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1903</v>
+        <v>-0.222</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2409</v>
+        <v>-0.1547</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2409</v>
+        <v>-0.1547</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4246</v>
+        <v>-0.4961</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3957</v>
+        <v>0.3959</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8203</v>
+        <v>-0.892</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4537</v>
+        <v>0.4327</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3181</v>
+        <v>0.2998</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4137</v>
+        <v>0.3921</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2781</v>
+        <v>0.2592</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3813</v>
+        <v>0.377</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3557</v>
+        <v>0.3553</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0255</v>
+        <v>0.0217</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5745</v>
+        <v>-0.6027</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2337</v>
+        <v>-1.1908</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6593</v>
+        <v>0.5881</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0194</v>
+        <v>-0.0618</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2868</v>
+        <v>0.2755</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3062</v>
+        <v>-0.3373</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.518</v>
+        <v>-0.5013</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4986</v>
+        <v>0.4396</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2069</v>
+        <v>0.1934</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2918</v>
+        <v>0.2461</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9552</v>
+        <v>-0.9304</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5157</v>
+        <v>-0.4947</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4395</v>
+        <v>-0.4357</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4222</v>
+        <v>-1.4226</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5578</v>
+        <v>-2.3632</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1356</v>
+        <v>0.9406</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.2776</v>
+        <v>-3.304</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3491</v>
+        <v>-1.3408</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9285</v>
+        <v>-1.9631</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.4681</v>
+        <v>-3.3739</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6341</v>
+        <v>-1.583</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.834</v>
+        <v>-1.7909</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1906</v>
+        <v>0.0699</v>
       </c>
       <c r="N8" t="n">
-        <v>0.285</v>
+        <v>0.2422</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0945</v>
+        <v>-0.1723</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2846</v>
+        <v>-1.2549</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2891</v>
+        <v>-1.2367</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0045</v>
+        <v>-0.0182</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1398</v>
+        <v>2.1626</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2846</v>
+        <v>-2.3559</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6009</v>
+        <v>-0.478</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6837</v>
+        <v>-1.8779</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0992</v>
+        <v>-1.1655</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3822</v>
+        <v>-1.3937</v>
       </c>
       <c r="I9" t="n">
-        <v>0.283</v>
+        <v>0.2282</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2763</v>
+        <v>-0.2222</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3963</v>
+        <v>-0.3437</v>
       </c>
       <c r="L9" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8229</v>
+        <v>-0.9433</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9859</v>
+        <v>-1.05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.163</v>
+        <v>0.1067</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4144</v>
+        <v>0.4201</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6162</v>
+        <v>1.6068</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2018</v>
+        <v>-1.1867</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7063</v>
+        <v>-2.6775</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6395</v>
+        <v>-1.2599</v>
       </c>
       <c r="F10" t="n">
+        <v>-1.4176</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6717</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.5585</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.8869</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.2859</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.3663</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.0804</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-2.6142</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.8078</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.8064</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.5842000000000001</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-4.0895</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3.5053</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-2.1545</v>
+      </c>
+      <c r="T10" t="n">
         <v>-1.0669</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.7072000000000001</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.5782</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1.871</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.0886</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.2791</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-0.1905</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-2.3814</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.7009</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-1.6805</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.6002</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-4.2012</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.601</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-2.2135</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-1.1268</v>
-      </c>
       <c r="U10" t="n">
-        <v>-1.0867</v>
+        <v>-1.0876</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7706</v>
+        <v>-6.8706</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1288</v>
+        <v>-4.922</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6418</v>
+        <v>-1.9486</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.3323</v>
+        <v>-4.4208</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3504</v>
+        <v>-0.4039</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.9819</v>
+        <v>-4.0169</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1303</v>
+        <v>-2.0315</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4217</v>
+        <v>0.4644</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.552</v>
+        <v>-2.4959</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.202</v>
+        <v>-2.3893</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7721</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4299</v>
+        <v>-1.521</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R11" t="n">
-        <v>3.0009</v>
+        <v>2.921</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.6183</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0024</v>
+        <v>0.0305</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.641</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.1289</v>
+        <v>-14.1072</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.2338</v>
+        <v>-9.077199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8951</v>
+        <v>-5.03</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.9981</v>
+        <v>-14.1843</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.423999999999999</v>
+        <v>-5.316000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.574</v>
+        <v>-8.8683</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.159600000000001</v>
+        <v>-2.0475</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.598</v>
+        <v>-0.9152000000000009</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5616</v>
+        <v>-1.1322</v>
       </c>
       <c r="M12" t="n">
-        <v>-10.8383</v>
+        <v>-12.1368</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.826</v>
+        <v>-4.401</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.012200000000001</v>
+        <v>-7.7361</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0003</v>
+        <v>0.9736000000000002</v>
       </c>
       <c r="Q12" t="n">
-        <v>-18.0052</v>
+        <v>-17.5262</v>
       </c>
       <c r="R12" t="n">
-        <v>19.0055</v>
+        <v>18.4999</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.2897</v>
+        <v>-3.1842</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4655</v>
+        <v>-0.2351999999999996</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.8244</v>
+        <v>-2.948799999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>2.1586</v>
+        <v>2.2874</v>
       </c>
       <c r="W12" t="n">
-        <v>10.3964</v>
+        <v>10.7316</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.238</v>
+        <v>-8.4443</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BOSCO MÉRIDA PATRIMONIO DE LA HUMANIDAD.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BOSCO MÉRIDA PATRIMONIO DE LA HUMANIDAD.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>J. RICARDO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4459</v>
+        <v>1.7614</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1139</v>
+        <v>2.6065</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5598</v>
+        <v>-0.8451</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.758</v>
+        <v>-2.4683</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.2257</v>
+        <v>-2.5672</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.5323</v>
+        <v>0.0989</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.2739</v>
+        <v>0.1328</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.3955</v>
+        <v>-1.6265</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1216</v>
+        <v>1.7594</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4841</v>
+        <v>-2.6011</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1698</v>
+        <v>-0.9407</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.6539</v>
+        <v>-1.6604</v>
       </c>
       <c r="P2" t="n">
+        <v>1.1684</v>
+      </c>
+      <c r="Q2" t="n">
         <v>-1.9474</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-3.8947</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.9474</v>
+        <v>3.1158</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3197</v>
+        <v>-0.5503</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3332</v>
+        <v>-0.4116</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9865</v>
+        <v>-0.1387</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8316</v>
+        <v>3.6116</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7216</v>
+        <v>4.8326</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.89</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RICARDO</t>
+          <t>A. GALLEGO CONTRERAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3273</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4104</v>
+        <v>-0.8917</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0831</v>
+        <v>0.9714</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.4683</v>
+        <v>-0.0618</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.5672</v>
+        <v>0.2755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0989</v>
+        <v>-0.3373</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1328</v>
+        <v>-0.5013</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.6265</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7594</v>
+        <v>-0.5835</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6011</v>
+        <v>0.4396</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9407</v>
+        <v>0.1934</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6604</v>
+        <v>0.2461</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1684</v>
+        <v>0.3895</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9474</v>
+        <v>-0.1947</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1158</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9844</v>
+        <v>-0.248</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.6077</v>
+        <v>-0.1957</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3767</v>
+        <v>-0.0524</v>
       </c>
       <c r="V3" t="n">
-        <v>3.6116</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>4.8326</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1727</v>
+        <v>-0.0452</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0413</v>
+        <v>0.0584</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1314</v>
+        <v>-0.1036</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3242</v>
@@ -766,13 +766,13 @@
         <v>0.1947</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0433</v>
+        <v>0.0842</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0618</v>
+        <v>0.0378</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0186</v>
+        <v>0.0464</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2823</v>
+        <v>-0.2345</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5144</v>
+        <v>-0.3151</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2321</v>
+        <v>0.0805</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7861</v>
@@ -844,13 +844,13 @@
         <v>3.1158</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3152</v>
+        <v>-0.2674</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.1062</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.222</v>
+        <v>-0.3736</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1547</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. RAMIREZ PRIETO</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4961</v>
+        <v>-0.2759</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3959</v>
+        <v>-1.5658</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.892</v>
+        <v>1.2899</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4327</v>
+        <v>-3.304</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1329</v>
+        <v>-1.3408</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2998</v>
+        <v>-1.9631</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0405</v>
+        <v>-3.3739</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-1.583</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>-1.7909</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3921</v>
+        <v>0.0699</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1329</v>
+        <v>0.2422</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2592</v>
+        <v>-0.1723</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1947</v>
+        <v>0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1947</v>
+        <v>1.1684</v>
       </c>
       <c r="S6" t="n">
-        <v>0.377</v>
+        <v>-0.1082</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3553</v>
+        <v>-0.4393</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0217</v>
+        <v>0.3311</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5005</v>
+        <v>2.1626</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.4421</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5005</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GALLEGO CONTRERAS</t>
+          <t>N. RAMIREZ PRIETO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6027</v>
+        <v>-0.656</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1908</v>
+        <v>0.0968</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5881</v>
+        <v>-0.7528</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0618</v>
+        <v>0.4327</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2755</v>
+        <v>0.1329</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3373</v>
+        <v>0.2998</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5013</v>
+        <v>0.0405</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08210000000000001</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5835</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4396</v>
+        <v>0.3921</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1934</v>
+        <v>0.1329</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2461</v>
+        <v>0.2592</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3895</v>
+        <v>0.1947</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1947</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.1947</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9304</v>
+        <v>0.2171</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4947</v>
+        <v>0.0563</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4357</v>
+        <v>0.1608</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4226</v>
+        <v>-1.1892</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3632</v>
+        <v>-1.7087</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9406</v>
+        <v>0.5195</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.304</v>
+        <v>-2.758</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3408</v>
+        <v>-1.2257</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9631</v>
+        <v>-1.5323</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.3739</v>
+        <v>-1.2739</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.583</v>
+        <v>-1.3955</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7909</v>
+        <v>0.1216</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0699</v>
+        <v>-1.4841</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2422</v>
+        <v>0.1698</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1723</v>
+        <v>-1.6539</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1947</v>
+        <v>-3.8947</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1684</v>
+        <v>1.9474</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2549</v>
+        <v>1.6846</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2367</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0182</v>
+        <v>0.9462</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1626</v>
+        <v>1.8316</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4421</v>
+        <v>2.7216</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2795</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3559</v>
+        <v>-1.4142</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.478</v>
+        <v>-0.5622</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8779</v>
+        <v>-0.852</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1655</v>
+        <v>0.6717</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3937</v>
+        <v>2.5585</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2282</v>
+        <v>-1.8869</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2222</v>
+        <v>3.2859</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3437</v>
+        <v>3.3663</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1216</v>
+        <v>-0.0804</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9433</v>
+        <v>-2.6142</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.05</v>
+        <v>-0.8078</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1067</v>
+        <v>-1.8064</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3895</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1421</v>
+        <v>-4.0895</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7526</v>
+        <v>3.5053</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4201</v>
+        <v>-0.8911</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6068</v>
+        <v>-0.3691</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1867</v>
+        <v>-0.5219</v>
       </c>
       <c r="V9" t="n">
+        <v>-0.6105</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.6105</v>
+      </c>
+      <c r="X9" t="n">
         <v>-1.2211</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.2795</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1.5005</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6775</v>
+        <v>-3.5628</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2599</v>
+        <v>-1.8734</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4176</v>
+        <v>-1.6894</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6717</v>
+        <v>-1.1655</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5585</v>
+        <v>-1.3937</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8869</v>
+        <v>0.2282</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2859</v>
+        <v>-0.2222</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3663</v>
+        <v>-0.3437</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0804</v>
+        <v>0.1216</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6142</v>
+        <v>-0.9433</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8078</v>
+        <v>-1.05</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8064</v>
+        <v>0.1067</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.0895</v>
+        <v>-2.1421</v>
       </c>
       <c r="R10" t="n">
-        <v>3.5053</v>
+        <v>1.7526</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1545</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0669</v>
+        <v>0.2114</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0876</v>
+        <v>-0.9982</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6105</v>
+        <v>-1.2211</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6105</v>
+        <v>0.2795</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2211</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8706</v>
+        <v>-6.577</v>
       </c>
       <c r="E11" t="n">
         <v>-4.922</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9486</v>
+        <v>-1.655</v>
       </c>
       <c r="G11" t="n">
         <v>-4.4208</v>
@@ -1312,13 +1312,13 @@
         <v>2.921</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6183</v>
+        <v>-0.3246</v>
       </c>
       <c r="T11" t="n">
         <v>0.0305</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.3551</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8316</v>
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.1072</v>
+        <v>-12.1137</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.077199999999999</v>
+        <v>-9.077200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.03</v>
+        <v>-3.0366</v>
       </c>
       <c r="G12" t="n">
         <v>-14.1843</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.316000000000001</v>
+        <v>-5.316</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.8683</v>
+        <v>-8.868299999999998</v>
       </c>
       <c r="J12" t="n">
         <v>-2.0475</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9152000000000009</v>
+        <v>-0.9152</v>
       </c>
       <c r="L12" t="n">
         <v>-1.1322</v>
@@ -1390,13 +1390,13 @@
         <v>18.4999</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.1842</v>
+        <v>-1.1905</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2351999999999996</v>
+        <v>-0.2351000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.948799999999999</v>
+        <v>-0.9554</v>
       </c>
       <c r="V12" t="n">
         <v>2.2874</v>
@@ -1405,7 +1405,7 @@
         <v>10.7316</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.4443</v>
+        <v>-8.444299999999998</v>
       </c>
     </row>
   </sheetData>
